--- a/GF_X-master/AAAGameData/Languages/Korean.xlsx
+++ b/GF_X-master/AAAGameData/Languages/Korean.xlsx
@@ -55,18 +55,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>BRAKE</t>
   </si>
   <si>
-    <t>중단</t>
+    <t>브레이크</t>
   </si>
   <si>
     <t>ENGINE</t>
   </si>
   <si>
     <t>엔진</t>
+  </si>
+  <si>
+    <t>FailGame</t>
+  </si>
+  <si>
+    <t>사장님한테 들키면 바로 쫓겨나고, 그 뒤로 길거리를 떠돌고, 클릭해서 다시 시간을 되돌려</t>
   </si>
   <si>
     <t>GET</t>
@@ -111,6 +117,12 @@
     <t>시작 클릭</t>
   </si>
   <si>
+    <t>Nice</t>
+  </si>
+  <si>
+    <t>잘했어!</t>
+  </si>
+  <si>
     <t>Nothing</t>
   </si>
   <si>
@@ -133,12 +145,6 @@
   </si>
   <si>
     <t>취소</t>
-  </si>
-  <si>
-    <t>RatingDialog.Description</t>
-  </si>
-  <si>
-    <t>이 게임 좋아해요?\n 별 다섯 개 호평해 주세요!</t>
   </si>
   <si>
     <t>RatingDialog.HighRatingTips</t>
@@ -228,6 +234,15 @@
     <t>STEERING</t>
   </si>
   <si>
+    <t>운전</t>
+  </si>
+  <si>
+    <t>SuccessGame</t>
+  </si>
+  <si>
+    <t>당신은 사장 딸의 마음을 사로잡는 데 성공하여, 즉시 백부미를 맞이하여, 이때부터 인생의 정점을 향해 나아갔다.</t>
+  </si>
+  <si>
     <t>TermsOfService</t>
   </si>
   <si>
@@ -237,13 +252,13 @@
     <t>Test123</t>
   </si>
   <si>
-    <t>언어 검색 테스트</t>
+    <t>코드 테스트 언어 검색</t>
   </si>
   <si>
-    <t>Test1234</t>
+    <t>TipStart</t>
   </si>
   <si>
-    <t/>
+    <t>샤오밍샤오메이를 클릭하여 키스하지만, 사장님이 보지 않도록 조심해라!그리고 문과 창문을 조심해라!</t>
   </si>
   <si>
     <t>UNLOCK</t>
@@ -404,6 +419,14 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -2819,6 +2842,1002 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -2835,265 +3854,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1058">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1058"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1059">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1059"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1060">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1060"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1061">
+            <xdr:cNvPr hidden="1" name="A1" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1061"/>
@@ -3168,18 +3929,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1062">
+            <xdr:cNvPr hidden="1" name="A2" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1062"/>
@@ -3254,18 +4015,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1063">
+            <xdr:cNvPr hidden="1" name="A3" id="1063">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1063"/>
@@ -3340,18 +4101,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1064">
+            <xdr:cNvPr hidden="1" name="A4" id="1064">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1064"/>
@@ -3426,18 +4187,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1065">
+            <xdr:cNvPr hidden="1" name="A5" id="1065">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1065"/>
@@ -3512,18 +4273,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1066">
+            <xdr:cNvPr hidden="1" name="A6" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1066"/>
@@ -3598,18 +4359,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1067">
+            <xdr:cNvPr hidden="1" name="A7" id="1067">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1067"/>
@@ -3684,18 +4445,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1068">
+            <xdr:cNvPr hidden="1" name="A8" id="1068">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1068"/>
@@ -3770,18 +4531,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1069">
+            <xdr:cNvPr hidden="1" name="A9" id="1069">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1069"/>
@@ -3856,18 +4617,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1070">
+            <xdr:cNvPr hidden="1" name="A10" id="1070">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1070"/>
@@ -3942,18 +4703,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1071">
+            <xdr:cNvPr hidden="1" name="A11" id="1071">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1071"/>
@@ -4028,18 +4789,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1072">
+            <xdr:cNvPr hidden="1" name="A12" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1072"/>
@@ -4114,18 +4875,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1073">
+            <xdr:cNvPr hidden="1" name="A13" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1073"/>
@@ -4200,18 +4961,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1074">
+            <xdr:cNvPr hidden="1" name="A14" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1074"/>
@@ -4286,18 +5047,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1075">
+            <xdr:cNvPr hidden="1" name="A15" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1075"/>
@@ -4372,18 +5133,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1076">
+            <xdr:cNvPr hidden="1" name="A16" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1076"/>
@@ -4458,18 +5219,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1077">
+            <xdr:cNvPr hidden="1" name="A17" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1077"/>
@@ -4544,18 +5305,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1078">
+            <xdr:cNvPr hidden="1" name="A18" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1078"/>
@@ -4630,18 +5391,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1079">
+            <xdr:cNvPr hidden="1" name="A19" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1079"/>
@@ -4716,18 +5477,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1080">
+            <xdr:cNvPr hidden="1" name="A20" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1080"/>
@@ -4802,18 +5563,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1081">
+            <xdr:cNvPr hidden="1" name="A21" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1081"/>
@@ -4888,18 +5649,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1082">
+            <xdr:cNvPr hidden="1" name="A22" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1082"/>
@@ -4974,18 +5735,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1083">
+            <xdr:cNvPr hidden="1" name="A23" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1083"/>
@@ -5060,18 +5821,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1084">
+            <xdr:cNvPr hidden="1" name="A24" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1084"/>
@@ -5146,18 +5907,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1085">
+            <xdr:cNvPr hidden="1" name="A25" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1085"/>
@@ -5232,18 +5993,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1086">
+            <xdr:cNvPr hidden="1" name="A26" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1086"/>
@@ -5318,18 +6079,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1087">
+            <xdr:cNvPr hidden="1" name="A27" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1087"/>
@@ -5404,18 +6165,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1088">
+            <xdr:cNvPr hidden="1" name="A28" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1088"/>
@@ -5490,18 +6251,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1089">
+            <xdr:cNvPr hidden="1" name="A29" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1089"/>
@@ -5576,18 +6337,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1090">
+            <xdr:cNvPr hidden="1" name="A30" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1090"/>
@@ -5656,12 +6417,442 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>30</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>31</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A31" id="1091">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1091"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>31</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>32</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A32" id="1092">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1092"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>32</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A33" id="1093">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>34</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A34" id="1094">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1094"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>34</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>35</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A35" id="1095">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1095"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -5927,43 +7118,61 @@
         <v>56</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1"/>
       <c r="B30" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1"/>
       <c r="B31" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1"/>
       <c r="B32" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1"/>
       <c r="B33" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1"/>
+      <c r="B34" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1"/>
+      <c r="B35" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -5975,7 +7184,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId576" name="A1">
+            <control shapeId="1061" r:id="rId818" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5997,7 +7206,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId577" name="A2">
+            <control shapeId="1062" r:id="rId819" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6019,7 +7228,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId578" name="A3">
+            <control shapeId="1063" r:id="rId820" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6041,7 +7250,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId579" name="A4">
+            <control shapeId="1064" r:id="rId821" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6063,7 +7272,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId580" name="A5">
+            <control shapeId="1065" r:id="rId822" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6085,7 +7294,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId581" name="A6">
+            <control shapeId="1066" r:id="rId823" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6107,7 +7316,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId582" name="A7">
+            <control shapeId="1067" r:id="rId824" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6129,7 +7338,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId583" name="A8">
+            <control shapeId="1068" r:id="rId825" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6151,7 +7360,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId584" name="A9">
+            <control shapeId="1069" r:id="rId826" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6173,7 +7382,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId585" name="A10">
+            <control shapeId="1070" r:id="rId827" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6195,7 +7404,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId586" name="A11">
+            <control shapeId="1071" r:id="rId828" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6217,7 +7426,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId587" name="A12">
+            <control shapeId="1072" r:id="rId829" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6239,7 +7448,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId588" name="A13">
+            <control shapeId="1073" r:id="rId830" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6261,7 +7470,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId589" name="A14">
+            <control shapeId="1074" r:id="rId831" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6283,7 +7492,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId590" name="A15">
+            <control shapeId="1075" r:id="rId832" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6305,7 +7514,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId591" name="A16">
+            <control shapeId="1076" r:id="rId833" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6327,7 +7536,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId592" name="A17">
+            <control shapeId="1077" r:id="rId834" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6349,7 +7558,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId593" name="A18">
+            <control shapeId="1078" r:id="rId835" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6371,7 +7580,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId594" name="A19">
+            <control shapeId="1079" r:id="rId836" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6393,7 +7602,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId595" name="A20">
+            <control shapeId="1080" r:id="rId837" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6415,7 +7624,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId596" name="A21">
+            <control shapeId="1081" r:id="rId838" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6437,7 +7646,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId597" name="A22">
+            <control shapeId="1082" r:id="rId839" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6459,7 +7668,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId598" name="A23">
+            <control shapeId="1083" r:id="rId840" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6481,7 +7690,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId599" name="A24">
+            <control shapeId="1084" r:id="rId841" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6503,7 +7712,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId600" name="A25">
+            <control shapeId="1085" r:id="rId842" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6525,7 +7734,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId601" name="A26">
+            <control shapeId="1086" r:id="rId843" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6547,7 +7756,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId602" name="A27">
+            <control shapeId="1087" r:id="rId844" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6569,7 +7778,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId603" name="A28">
+            <control shapeId="1088" r:id="rId845" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6591,7 +7800,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId604" name="A29">
+            <control shapeId="1089" r:id="rId846" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6613,7 +7822,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId605" name="A30">
+            <control shapeId="1090" r:id="rId847" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6635,7 +7844,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId606" name="A31">
+            <control shapeId="1091" r:id="rId848" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6657,7 +7866,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId607" name="A32">
+            <control shapeId="1092" r:id="rId849" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6679,7 +7888,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId608" name="A33">
+            <control shapeId="1093" r:id="rId850" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6699,6 +7908,50 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1094" r:id="rId851" name="A34">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>33</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>34</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1095" r:id="rId852" name="A35">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>34</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>35</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/GF_X-master/AAAGameData/Languages/Korean.xlsx
+++ b/GF_X-master/AAAGameData/Languages/Korean.xlsx
@@ -3838,6 +3838,286 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -3854,7 +4134,93 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1061">
+            <xdr:cNvPr hidden="1" name="A1" id="1060">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1060"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A2" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1061"/>
@@ -3929,18 +4295,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1062">
+            <xdr:cNvPr hidden="1" name="A3" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1062"/>
@@ -4015,18 +4381,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1063">
+            <xdr:cNvPr hidden="1" name="A4" id="1063">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1063"/>
@@ -4101,18 +4467,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1064">
+            <xdr:cNvPr hidden="1" name="A5" id="1064">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1064"/>
@@ -4187,18 +4553,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1065">
+            <xdr:cNvPr hidden="1" name="A6" id="1065">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1065"/>
@@ -4273,18 +4639,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1066">
+            <xdr:cNvPr hidden="1" name="A7" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1066"/>
@@ -4359,18 +4725,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1067">
+            <xdr:cNvPr hidden="1" name="A8" id="1067">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1067"/>
@@ -4445,18 +4811,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1068">
+            <xdr:cNvPr hidden="1" name="A9" id="1068">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1068"/>
@@ -4531,18 +4897,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1069">
+            <xdr:cNvPr hidden="1" name="A10" id="1069">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1069"/>
@@ -4617,18 +4983,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1070">
+            <xdr:cNvPr hidden="1" name="A11" id="1070">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1070"/>
@@ -4703,18 +5069,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1071">
+            <xdr:cNvPr hidden="1" name="A12" id="1071">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1071"/>
@@ -4789,18 +5155,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1072">
+            <xdr:cNvPr hidden="1" name="A13" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1072"/>
@@ -4875,18 +5241,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1073">
+            <xdr:cNvPr hidden="1" name="A14" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1073"/>
@@ -4961,18 +5327,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1074">
+            <xdr:cNvPr hidden="1" name="A15" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1074"/>
@@ -5047,18 +5413,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1075">
+            <xdr:cNvPr hidden="1" name="A16" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1075"/>
@@ -5133,18 +5499,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1076">
+            <xdr:cNvPr hidden="1" name="A17" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1076"/>
@@ -5219,18 +5585,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1077">
+            <xdr:cNvPr hidden="1" name="A18" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1077"/>
@@ -5305,18 +5671,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1078">
+            <xdr:cNvPr hidden="1" name="A19" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1078"/>
@@ -5391,18 +5757,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1079">
+            <xdr:cNvPr hidden="1" name="A20" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1079"/>
@@ -5477,18 +5843,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1080">
+            <xdr:cNvPr hidden="1" name="A21" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1080"/>
@@ -5563,18 +5929,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1081">
+            <xdr:cNvPr hidden="1" name="A22" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1081"/>
@@ -5649,18 +6015,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1082">
+            <xdr:cNvPr hidden="1" name="A23" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1082"/>
@@ -5735,18 +6101,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1083">
+            <xdr:cNvPr hidden="1" name="A24" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1083"/>
@@ -5821,18 +6187,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1084">
+            <xdr:cNvPr hidden="1" name="A25" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1084"/>
@@ -5907,18 +6273,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1085">
+            <xdr:cNvPr hidden="1" name="A26" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1085"/>
@@ -5993,18 +6359,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1086">
+            <xdr:cNvPr hidden="1" name="A27" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1086"/>
@@ -6079,18 +6445,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1087">
+            <xdr:cNvPr hidden="1" name="A28" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1087"/>
@@ -6165,18 +6531,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1088">
+            <xdr:cNvPr hidden="1" name="A29" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1088"/>
@@ -6251,18 +6617,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1089">
+            <xdr:cNvPr hidden="1" name="A30" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1089"/>
@@ -6337,18 +6703,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1090">
+            <xdr:cNvPr hidden="1" name="A31" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1090"/>
@@ -6423,18 +6789,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1091">
+            <xdr:cNvPr hidden="1" name="A32" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1091"/>
@@ -6509,18 +6875,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1092">
+            <xdr:cNvPr hidden="1" name="A33" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1092"/>
@@ -6595,18 +6961,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1093">
+            <xdr:cNvPr hidden="1" name="A34" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1093"/>
@@ -6681,92 +7047,6 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1094">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1094"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
           <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -6778,10 +7058,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1095">
+            <xdr:cNvPr hidden="1" name="A35" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1095"/>
+                  <a14:compatExt spid="_x0000_s1094"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7184,7 +7464,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId818" name="A1">
+            <control shapeId="1060" r:id="rId886" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7206,7 +7486,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId819" name="A2">
+            <control shapeId="1061" r:id="rId887" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7228,7 +7508,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId820" name="A3">
+            <control shapeId="1062" r:id="rId888" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7250,7 +7530,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId821" name="A4">
+            <control shapeId="1063" r:id="rId889" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7272,7 +7552,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId822" name="A5">
+            <control shapeId="1064" r:id="rId890" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7294,7 +7574,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId823" name="A6">
+            <control shapeId="1065" r:id="rId891" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7316,7 +7596,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId824" name="A7">
+            <control shapeId="1066" r:id="rId892" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7338,7 +7618,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId825" name="A8">
+            <control shapeId="1067" r:id="rId893" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7360,7 +7640,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId826" name="A9">
+            <control shapeId="1068" r:id="rId894" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7382,7 +7662,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId827" name="A10">
+            <control shapeId="1069" r:id="rId895" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7404,7 +7684,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId828" name="A11">
+            <control shapeId="1070" r:id="rId896" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7426,7 +7706,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId829" name="A12">
+            <control shapeId="1071" r:id="rId897" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7448,7 +7728,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId830" name="A13">
+            <control shapeId="1072" r:id="rId898" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7470,7 +7750,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId831" name="A14">
+            <control shapeId="1073" r:id="rId899" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7492,7 +7772,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId832" name="A15">
+            <control shapeId="1074" r:id="rId900" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7514,7 +7794,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId833" name="A16">
+            <control shapeId="1075" r:id="rId901" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7536,7 +7816,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId834" name="A17">
+            <control shapeId="1076" r:id="rId902" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7558,7 +7838,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId835" name="A18">
+            <control shapeId="1077" r:id="rId903" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7580,7 +7860,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId836" name="A19">
+            <control shapeId="1078" r:id="rId904" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7602,7 +7882,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId837" name="A20">
+            <control shapeId="1079" r:id="rId905" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7624,7 +7904,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId838" name="A21">
+            <control shapeId="1080" r:id="rId906" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7646,7 +7926,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId839" name="A22">
+            <control shapeId="1081" r:id="rId907" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7668,7 +7948,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId840" name="A23">
+            <control shapeId="1082" r:id="rId908" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7690,7 +7970,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId841" name="A24">
+            <control shapeId="1083" r:id="rId909" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7712,7 +7992,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId842" name="A25">
+            <control shapeId="1084" r:id="rId910" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7734,7 +8014,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId843" name="A26">
+            <control shapeId="1085" r:id="rId911" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7756,7 +8036,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId844" name="A27">
+            <control shapeId="1086" r:id="rId912" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7778,7 +8058,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId845" name="A28">
+            <control shapeId="1087" r:id="rId913" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7800,7 +8080,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId846" name="A29">
+            <control shapeId="1088" r:id="rId914" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7822,7 +8102,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId847" name="A30">
+            <control shapeId="1089" r:id="rId915" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7844,7 +8124,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId848" name="A31">
+            <control shapeId="1090" r:id="rId916" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7866,7 +8146,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId849" name="A32">
+            <control shapeId="1091" r:id="rId917" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7888,7 +8168,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId850" name="A33">
+            <control shapeId="1092" r:id="rId918" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7910,7 +8190,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId851" name="A34">
+            <control shapeId="1093" r:id="rId919" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7932,7 +8212,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId852" name="A35">
+            <control shapeId="1094" r:id="rId920" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
